--- a/config/组合测控/干式变压器温湿度控制器.xlsx
+++ b/config/组合测控/干式变压器温湿度控制器.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>序号</t>
   </si>
@@ -108,25 +108,6 @@
   </si>
   <si>
     <t>routeDTemperature</t>
-  </si>
-  <si>
-    <t>继电器数据状态</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>bit0:风机运行
-bit1:超温跳闸
-bit2:超温报警
-bit3:故障报警
-bit4:保留
-bit5:风机故障
-bit6:加热除湿
-bit7:门接触点状态</t>
-  </si>
-  <si>
-    <t>status</t>
   </si>
 </sst>
 </file>
@@ -772,7 +753,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -787,15 +768,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1322,8 +1294,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelRow="5"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="13.8968253968254" customWidth="1"/>
     <col min="5" max="5" width="18.3333333333333" customWidth="1"/>
@@ -1510,42 +1482,6 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="144" spans="1:16">
-      <c r="A6" s="3">
-        <v>2000</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="7"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/config/组合测控/干式变压器温湿度控制器.xlsx
+++ b/config/组合测控/干式变压器温湿度控制器.xlsx
@@ -83,7 +83,7 @@
     <t>I16</t>
   </si>
   <si>
-    <t>InputRegisters</t>
+    <t>HoldingRegisters</t>
   </si>
   <si>
     <t>AB</t>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,13 +132,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -623,137 +616,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -764,9 +757,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1299,7 +1289,8 @@
   <cols>
     <col min="2" max="2" width="13.8968253968254" customWidth="1"/>
     <col min="5" max="5" width="18.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="14.3888888888889" customWidth="1"/>
+    <col min="7" max="7" width="16.7222222222222" customWidth="1"/>
+    <col min="9" max="9" width="16.3333333333333" customWidth="1"/>
     <col min="13" max="13" width="19.4920634920635" customWidth="1"/>
     <col min="14" max="14" width="11.968253968254" customWidth="1"/>
   </cols>
@@ -1399,7 +1390,7 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="2">
